--- a/artfynd/A 61860-2024 artfynd.xlsx
+++ b/artfynd/A 61860-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121745576</v>
+        <v>121745564</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555009</v>
+        <v>554988</v>
       </c>
       <c r="R2" t="n">
-        <v>6400938</v>
+        <v>6400932</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121745564</v>
+        <v>121745576</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554988</v>
+        <v>555009</v>
       </c>
       <c r="R3" t="n">
-        <v>6400932</v>
+        <v>6400938</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 61860-2024 artfynd.xlsx
+++ b/artfynd/A 61860-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121745564</v>
+        <v>121745576</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554988</v>
+        <v>555009</v>
       </c>
       <c r="R2" t="n">
-        <v>6400932</v>
+        <v>6400938</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121745576</v>
+        <v>121745564</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555009</v>
+        <v>554988</v>
       </c>
       <c r="R3" t="n">
-        <v>6400938</v>
+        <v>6400932</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 61860-2024 artfynd.xlsx
+++ b/artfynd/A 61860-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121745576</v>
+        <v>121745991</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555009</v>
+        <v>555211</v>
       </c>
       <c r="R2" t="n">
-        <v>6400938</v>
+        <v>6400808</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121745564</v>
+        <v>121745576</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554988</v>
+        <v>555009</v>
       </c>
       <c r="R3" t="n">
-        <v>6400932</v>
+        <v>6400938</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121745991</v>
+        <v>121745564</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555211</v>
+        <v>554988</v>
       </c>
       <c r="R4" t="n">
-        <v>6400808</v>
+        <v>6400932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61860-2024 artfynd.xlsx
+++ b/artfynd/A 61860-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121745991</v>
+        <v>121745564</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555211</v>
+        <v>554988</v>
       </c>
       <c r="R2" t="n">
-        <v>6400808</v>
+        <v>6400932</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121745576</v>
+        <v>121745991</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555009</v>
+        <v>555211</v>
       </c>
       <c r="R3" t="n">
-        <v>6400938</v>
+        <v>6400808</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121745564</v>
+        <v>121745576</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554988</v>
+        <v>555009</v>
       </c>
       <c r="R4" t="n">
-        <v>6400932</v>
+        <v>6400938</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61860-2024 artfynd.xlsx
+++ b/artfynd/A 61860-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121745564</v>
+        <v>121745991</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554988</v>
+        <v>555211</v>
       </c>
       <c r="R2" t="n">
-        <v>6400932</v>
+        <v>6400808</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121745991</v>
+        <v>121745576</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555211</v>
+        <v>555009</v>
       </c>
       <c r="R3" t="n">
-        <v>6400808</v>
+        <v>6400938</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121745576</v>
+        <v>121745564</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555009</v>
+        <v>554988</v>
       </c>
       <c r="R4" t="n">
-        <v>6400938</v>
+        <v>6400932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61860-2024 artfynd.xlsx
+++ b/artfynd/A 61860-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121745991</v>
+        <v>121745564</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555211</v>
+        <v>554988</v>
       </c>
       <c r="R2" t="n">
-        <v>6400808</v>
+        <v>6400932</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,7 +803,7 @@
         <v>121745576</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121745564</v>
+        <v>121745991</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554988</v>
+        <v>555211</v>
       </c>
       <c r="R4" t="n">
-        <v>6400932</v>
+        <v>6400808</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61860-2024 artfynd.xlsx
+++ b/artfynd/A 61860-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121745564</v>
+        <v>121745576</v>
       </c>
       <c r="B2" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554988</v>
+        <v>555009</v>
       </c>
       <c r="R2" t="n">
-        <v>6400932</v>
+        <v>6400938</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121745576</v>
+        <v>121745564</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555009</v>
+        <v>554988</v>
       </c>
       <c r="R3" t="n">
-        <v>6400938</v>
+        <v>6400932</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +928,7 @@
         <v>121745991</v>
       </c>
       <c r="B4" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 61860-2024 artfynd.xlsx
+++ b/artfynd/A 61860-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121745576</v>
       </c>
       <c r="B2" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>121745564</v>
       </c>
       <c r="B3" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>121745991</v>
       </c>
       <c r="B4" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 61860-2024 artfynd.xlsx
+++ b/artfynd/A 61860-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121745576</v>
+        <v>121745564</v>
       </c>
       <c r="B2" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555009</v>
+        <v>554988</v>
       </c>
       <c r="R2" t="n">
-        <v>6400938</v>
+        <v>6400932</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121745564</v>
+        <v>121745576</v>
       </c>
       <c r="B3" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554988</v>
+        <v>555009</v>
       </c>
       <c r="R3" t="n">
-        <v>6400932</v>
+        <v>6400938</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +928,7 @@
         <v>121745991</v>
       </c>
       <c r="B4" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 61860-2024 artfynd.xlsx
+++ b/artfynd/A 61860-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121745991</v>
+        <v>121745564</v>
       </c>
       <c r="B2" t="n">
-        <v>98157</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555211</v>
+        <v>554988</v>
       </c>
       <c r="R2" t="n">
-        <v>6400808</v>
+        <v>6400932</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121745564</v>
+        <v>121745576</v>
       </c>
       <c r="B3" t="n">
-        <v>98157</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554988</v>
+        <v>555009</v>
       </c>
       <c r="R3" t="n">
-        <v>6400932</v>
+        <v>6400938</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121745576</v>
+        <v>121745991</v>
       </c>
       <c r="B4" t="n">
-        <v>98157</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +945,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555009</v>
+        <v>555211</v>
       </c>
       <c r="R4" t="n">
-        <v>6400938</v>
+        <v>6400808</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61860-2024 artfynd.xlsx
+++ b/artfynd/A 61860-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121745564</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121745576</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,8 +1047,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121745991</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>